--- a/public/exports-60-250-with-coowners/55606617.xlsx
+++ b/public/exports-60-250-with-coowners/55606617.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 6</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,20 +1326,20 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J18">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669682</t>
+          <t xml:space="preserve">311669685</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Idrætsvej 88</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,20 +1401,20 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">2079345</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J19">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669685</t>
+          <t xml:space="preserve">311669680</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 88</t>
+          <t xml:space="preserve">Plovheldvej 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1476,20 +1476,20 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2079345</t>
+          <t xml:space="preserve">2023800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J20">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669680</t>
+          <t xml:space="preserve">311669678</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plovheldvej 2</t>
+          <t xml:space="preserve">Risbjergvej 20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,20 +1551,20 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023800</t>
+          <t xml:space="preserve">2090722</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J21">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669678</t>
+          <t xml:space="preserve">311669679</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risbjergvej 20</t>
+          <t xml:space="preserve">Byvej 98</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2090722</t>
+          <t xml:space="preserve">7029060</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J22">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669679</t>
+          <t xml:space="preserve">311670169</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 98</t>
+          <t xml:space="preserve">Hovedporten 1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1701,20 +1701,20 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7029060</t>
+          <t xml:space="preserve">8490056</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J23">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670169</t>
+          <t xml:space="preserve">311670178</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydenhøjstien 2</t>
+          <t xml:space="preserve">Hovedporten 2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,20 +1776,20 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2159169</t>
+          <t xml:space="preserve">8490057</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J24">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670404</t>
+          <t xml:space="preserve">311670173</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedporten 1</t>
+          <t xml:space="preserve">M Bechs Alle 122</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,20 +1851,20 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490056</t>
+          <t xml:space="preserve">2025107</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J25">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670178</t>
+          <t xml:space="preserve">311670133</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedporten 2</t>
+          <t xml:space="preserve">Østre Messegade 3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,20 +1926,20 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490057</t>
+          <t xml:space="preserve">9889328</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J26">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670173</t>
+          <t xml:space="preserve">311670118</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">M Bechs Alle 122</t>
+          <t xml:space="preserve">Høvedstensvej 47</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,20 +2001,20 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025107</t>
+          <t xml:space="preserve">2091204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J27">
-        <v>108</v>
+        <v>246</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670133</t>
+          <t xml:space="preserve">311674027</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Messegade 3</t>
+          <t xml:space="preserve">Bibliotekvej 52A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,30 +2076,30 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9889328</t>
+          <t xml:space="preserve">100191021</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J28">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670118</t>
+          <t xml:space="preserve">311740622</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2034-02-22</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 47</t>
+          <t xml:space="preserve">Bibliotekvej 60C</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2151,20 +2151,20 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091204</t>
+          <t xml:space="preserve">2091215</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J29">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674027</t>
+          <t xml:space="preserve">311814926</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-17</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 52A</t>
+          <t xml:space="preserve">Bytoften 29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,30 +2226,30 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">100191021</t>
+          <t xml:space="preserve">2025808</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J30">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740622</t>
+          <t xml:space="preserve">311814922</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-22</t>
+          <t xml:space="preserve">2035-03-03</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekvej 60C</t>
+          <t xml:space="preserve">Byvej 118</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091215</t>
+          <t xml:space="preserve">2157369</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="J31">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814926</t>
+          <t xml:space="preserve">311814933</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,35 +2361,35 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 29</t>
+          <t xml:space="preserve">Ericavej 2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">4560</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025808</t>
+          <t xml:space="preserve">2449037</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814922</t>
+          <t xml:space="preserve">311814927</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2436,35 +2436,35 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">167</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 118</t>
+          <t xml:space="preserve">Ericavej 2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">4560</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2157369</t>
+          <t xml:space="preserve">2449037</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>230</v>
+        <v>131</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814933</t>
+          <t xml:space="preserve">311814927</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2531,11 +2531,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J34">
-        <v>131</v>
+        <v>247</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2606,11 +2606,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J35">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J36">
-        <v>247</v>
+        <v>137</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2736,35 +2736,35 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ericavej 2</t>
+          <t xml:space="preserve">Hvidovregade 20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4560</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2449037</t>
+          <t xml:space="preserve">2025809</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814927</t>
+          <t xml:space="preserve">311814925</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2811,35 +2811,35 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ericavej 2</t>
+          <t xml:space="preserve">Hvidovregade 20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4560</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2449037</t>
+          <t xml:space="preserve">2025809</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J38">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814927</t>
+          <t xml:space="preserve">311814925</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J39">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 20</t>
+          <t xml:space="preserve">Næsborgvej 90</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,20 +2976,20 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025809</t>
+          <t xml:space="preserve">7028766</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814925</t>
+          <t xml:space="preserve">311814924</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovregade 20</t>
+          <t xml:space="preserve">Egevolden 106</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025809</t>
+          <t xml:space="preserve">2160102</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>98</v>
+        <v>237</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814925</t>
+          <t xml:space="preserve">311897781</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næsborgvej 90</t>
+          <t xml:space="preserve">Hvidovrevej 218</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,20 +3126,20 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028766</t>
+          <t xml:space="preserve">7028740</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J42">
-        <v>218</v>
+        <v>160</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814924</t>
+          <t xml:space="preserve">311903570</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-03</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevolden 106</t>
+          <t xml:space="preserve">Høvedstensvej 19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,20 +3201,20 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160102</t>
+          <t xml:space="preserve">2091170</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J43">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897781</t>
+          <t xml:space="preserve">311903573</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-05-26</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvidovrevej 218</t>
+          <t xml:space="preserve">Næsborgvej 92</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,20 +3276,20 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">7028740</t>
+          <t xml:space="preserve">2025854</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903570</t>
+          <t xml:space="preserve">311903572</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høvedstensvej 19</t>
+          <t xml:space="preserve">Frydenhøjstien 2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,30 +3351,30 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091170</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J45">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903573</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næsborgvej 92</t>
+          <t xml:space="preserve">Frydenhøjstien 6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,30 +3426,30 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025854</t>
+          <t xml:space="preserve">2159169</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J46">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903572</t>
+          <t xml:space="preserve">311930507</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-26</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
